--- a/uploads/invalid_data.xlsx
+++ b/uploads/invalid_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>TEL CLIENT</t>
   </si>
@@ -25,10 +25,10 @@
     <t xml:space="preserve"> MNT IMP</t>
   </si>
   <si>
-    <t>061125047</t>
-  </si>
-  <si>
-    <t>02323</t>
+    <t>61125047</t>
+  </si>
+  <si>
+    <t>2323</t>
   </si>
   <si>
     <t>0661250473</t>
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -430,20 +430,9 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>3174265</v>
+        <v>3128871</v>
       </c>
       <c r="C4">
-        <v>18924.38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3128871</v>
-      </c>
-      <c r="C5">
         <v>16666.51</v>
       </c>
     </row>
